--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484673_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484673_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LORENTE</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2022</v>
+        <v>2.0026</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2987</v>
+        <v>1.7913</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9035</v>
+        <v>0.2113</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1824</v>
+        <v>2.622</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3791</v>
+        <v>2.5612</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5615</v>
+        <v>0.0608</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1781</v>
+        <v>3.1217</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1363</v>
+        <v>2.195</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0419</v>
+        <v>0.9267</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.3605</v>
+        <v>-0.4997</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7572</v>
+        <v>0.3662</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.6033</v>
+        <v>-0.8659</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0158</v>
+        <v>-1.8326</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3823</v>
+        <v>2.0158</v>
       </c>
       <c r="S2" t="n">
-        <v>0.751</v>
+        <v>0.1423</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4925</v>
+        <v>1.1252</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2586</v>
+        <v>-0.9829</v>
       </c>
       <c r="V2" t="n">
-        <v>1.267</v>
+        <v>-0.945</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6439</v>
+        <v>-0.6231</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>V. PRADA SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3018</v>
+        <v>1.4679</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2143</v>
+        <v>1.4417</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0261</v>
       </c>
       <c r="G3" t="n">
-        <v>2.622</v>
+        <v>3.2694</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5612</v>
+        <v>-1.4974</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0608</v>
+        <v>4.7668</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1217</v>
+        <v>4.1705</v>
       </c>
       <c r="K3" t="n">
-        <v>2.195</v>
+        <v>-1.1737</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9267</v>
+        <v>5.3442</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4997</v>
+        <v>-0.9011</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3662</v>
+        <v>-0.3237</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8659</v>
+        <v>-0.5774</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1833</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8326</v>
+        <v>-3.8484</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0158</v>
+        <v>1.4661</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5584</v>
+        <v>-0.0735</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5483</v>
+        <v>0.4653</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1067</v>
+        <v>-0.5389</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.945</v>
+        <v>0.6543</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6231</v>
+        <v>0.6543</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. PRADA SANCHEZ</t>
+          <t>J. JIMENEZ LORENTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0278</v>
+        <v>1.1953</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2494</v>
+        <v>1.0102</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2216</v>
+        <v>0.1851</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2694</v>
+        <v>-0.1824</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4974</v>
+        <v>0.3791</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7668</v>
+        <v>-0.5615</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1705</v>
+        <v>2.1781</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.1737</v>
+        <v>1.1363</v>
       </c>
       <c r="L4" t="n">
-        <v>5.3442</v>
+        <v>1.0419</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9011</v>
+        <v>-2.3605</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3237</v>
+        <v>-0.7572</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5774</v>
+        <v>-1.6033</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.3823</v>
+        <v>0.3665</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.8484</v>
+        <v>-2.0158</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4661</v>
+        <v>2.3823</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.2559</v>
       </c>
       <c r="T4" t="n">
-        <v>0.273</v>
+        <v>0.204</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7866</v>
+        <v>-0.4599</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6543</v>
+        <v>1.267</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6543</v>
+        <v>0.6439</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="5">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9288999999999999</v>
+        <v>1.1212</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2843</v>
+        <v>1.4766</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3554</v>
@@ -844,10 +844,10 @@
         <v>0.1833</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3115</v>
+        <v>-0.1192</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0551</v>
+        <v>0.1373</v>
       </c>
       <c r="U5" t="n">
         <v>-0.2564</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4233</v>
+        <v>0.5997</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7015</v>
+        <v>3.6054</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.2782</v>
+        <v>-3.0057</v>
       </c>
       <c r="G6" t="n">
         <v>0.7183</v>
@@ -922,13 +922,13 @@
         <v>0.5498</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6615</v>
+        <v>-0.4851</v>
       </c>
       <c r="T6" t="n">
-        <v>0.365</v>
+        <v>0.2689</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0265</v>
+        <v>-0.754</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0215</v>
+        <v>-0.7506</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4261</v>
+        <v>0.753</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4045</v>
+        <v>-1.5036</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9644</v>
@@ -1000,13 +1000,13 @@
         <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8314</v>
+        <v>0.0592</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4819</v>
+        <v>0.8088</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6505</v>
+        <v>-0.7496</v>
       </c>
       <c r="V7" t="n">
         <v>-0.945</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. RUEDA RIOS</t>
+          <t>S. HERRANDO CUENCA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9648</v>
+        <v>-2.1602</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4562</v>
+        <v>-2.9867</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5086</v>
+        <v>0.8266</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7101</v>
+        <v>-0.5689</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6553</v>
+        <v>-1.6362</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3654</v>
+        <v>1.0673</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6901</v>
+        <v>-0.6463</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4522</v>
+        <v>-2.1306</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2379</v>
+        <v>1.4844</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4002</v>
+        <v>0.0774</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7968</v>
+        <v>0.4944</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6033</v>
+        <v>-0.417</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5498</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.7489</v>
+        <v>-3.8484</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1991</v>
+        <v>1.0995</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.383</v>
+        <v>-0.7325</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6026</v>
+        <v>0.241</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9856</v>
+        <v>-0.9734</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3219</v>
+        <v>1.89</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3219</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. HERRANDO CUENCA</t>
+          <t>H. RUEDA RIOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1325</v>
+        <v>-2.278</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0829</v>
+        <v>-0.7446</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9504</v>
+        <v>-1.5334</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5689</v>
+        <v>-0.7101</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6362</v>
+        <v>0.6553</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0673</v>
+        <v>-1.3654</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6463</v>
+        <v>1.6901</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.1306</v>
+        <v>1.4522</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4844</v>
+        <v>0.2379</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0774</v>
+        <v>-2.4002</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4944</v>
+        <v>-0.7968</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.417</v>
+        <v>-1.6033</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.5498</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-2.7489</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-3.8484</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.0995</v>
+        <v>2.1991</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7048</v>
+        <v>-0.6963</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1448</v>
+        <v>0.3141</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8496</v>
+        <v>-1.0104</v>
       </c>
       <c r="V9" t="n">
-        <v>1.89</v>
+        <v>-0.3219</v>
       </c>
       <c r="W9" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.828</v>
+        <v>-2.7478</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8899</v>
+        <v>-1.0823</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.938</v>
+        <v>-1.6655</v>
       </c>
       <c r="G10" t="n">
         <v>-1.291</v>
@@ -1234,13 +1234,13 @@
         <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>0.785</v>
+        <v>0.8652</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1162</v>
+        <v>0.9238</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3312</v>
+        <v>-0.0586</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5889</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8581</v>
+        <v>-4.3278</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7902</v>
+        <v>-2.3095</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0679</v>
+        <v>-2.0183</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1506</v>
@@ -1312,13 +1312,13 @@
         <v>1.4661</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1578</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3122</v>
+        <v>0.1686</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8456</v>
+        <v>-0.796</v>
       </c>
       <c r="V11" t="n">
         <v>-1.267</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8779</v>
+        <v>-5.877699999999999</v>
       </c>
       <c r="E12" t="n">
         <v>2.955099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.832800000000001</v>
+        <v>-8.832799999999999</v>
       </c>
       <c r="G12" t="n">
         <v>3.121300000000001</v>
@@ -1360,13 +1360,13 @@
         <v>-2.1676</v>
       </c>
       <c r="I12" t="n">
-        <v>5.288799999999999</v>
+        <v>5.288800000000001</v>
       </c>
       <c r="J12" t="n">
         <v>14.0089</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2585000000000003</v>
+        <v>-0.2584999999999998</v>
       </c>
       <c r="L12" t="n">
         <v>14.2679</v>
@@ -1390,13 +1390,13 @@
         <v>13.7443</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9232</v>
+        <v>-1.9233</v>
       </c>
       <c r="T12" t="n">
-        <v>4.657</v>
+        <v>4.656999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.5801</v>
+        <v>-6.580100000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5784</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2432</v>
+        <v>3.0864</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9539</v>
+        <v>2.5116</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2893</v>
+        <v>0.5748</v>
       </c>
       <c r="G13" t="n">
         <v>0.6163</v>
@@ -1468,13 +1468,13 @@
         <v>2.3823</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3887</v>
+        <v>1.2319</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6358</v>
+        <v>1.1935</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2471</v>
+        <v>0.0384</v>
       </c>
       <c r="V13" t="n">
         <v>0.3219</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.963</v>
+        <v>2.2155</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8807</v>
+        <v>2.0396</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0823</v>
+        <v>0.1758</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4662</v>
+        <v>0.2275</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1176</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5837</v>
+        <v>0.8399</v>
       </c>
       <c r="J14" t="n">
-        <v>0.386</v>
+        <v>1.4718</v>
       </c>
       <c r="K14" t="n">
-        <v>0.136</v>
+        <v>-0.5543</v>
       </c>
       <c r="L14" t="n">
-        <v>0.25</v>
+        <v>2.0261</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8522</v>
+        <v>-1.2443</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0184</v>
+        <v>-0.0581</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8338</v>
+        <v>-1.1863</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3665</v>
+        <v>1.6493</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>1.6493</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8507</v>
+        <v>0.0272</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9216</v>
+        <v>0.2459</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0709</v>
+        <v>-0.2187</v>
       </c>
       <c r="V14" t="n">
-        <v>0.945</v>
+        <v>0.3115</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5889</v>
+        <v>0.3219</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6439</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="15">
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9975000000000001</v>
+        <v>1.8781</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0781</v>
+        <v>1.4708</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0806</v>
+        <v>0.4073</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2275</v>
+        <v>0.49</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6124000000000001</v>
+        <v>0.4801</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8399</v>
+        <v>0.0098</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4718</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5543</v>
+        <v>0.065</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0261</v>
+        <v>0.8115</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2443</v>
+        <v>-0.3866</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0581</v>
+        <v>0.4151</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1863</v>
+        <v>-0.8017</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1908</v>
+        <v>0.1054</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7157</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4751</v>
+        <v>-0.4889</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. CAPOUE</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8823</v>
+        <v>1.555</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2515</v>
+        <v>1.2076</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1338</v>
+        <v>0.3474</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5765</v>
+        <v>-0.4662</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7568</v>
+        <v>0.1176</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3333</v>
+        <v>-0.5837</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1427</v>
+        <v>0.386</v>
       </c>
       <c r="K17" t="n">
-        <v>0.421</v>
+        <v>0.136</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5637</v>
+        <v>0.25</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4338</v>
+        <v>-0.8522</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3357</v>
+        <v>-0.0184</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7695</v>
+        <v>-0.8338</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3665</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1369</v>
+        <v>1.4427</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1637</v>
+        <v>1.2485</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0268</v>
+        <v>0.1942</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9554</v>
+        <v>0.945</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6439</v>
+        <v>1.5889</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3115</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4786</v>
+        <v>1.344</v>
       </c>
       <c r="E18" t="n">
-        <v>1.377</v>
+        <v>1.8578</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8984</v>
+        <v>-0.5138</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1081</v>
@@ -1858,13 +1858,13 @@
         <v>2.3823</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3296</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1267</v>
+        <v>0.6075</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4563</v>
+        <v>-0.0717</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>E. CAPOUE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3381</v>
+        <v>1.3267</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5093</v>
+        <v>-0.0591</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1711</v>
+        <v>1.3858</v>
       </c>
       <c r="G19" t="n">
-        <v>0.49</v>
+        <v>-0.5765</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4801</v>
+        <v>0.7568</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0098</v>
+        <v>-1.3333</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8764999999999999</v>
+        <v>-0.1427</v>
       </c>
       <c r="K19" t="n">
-        <v>0.065</v>
+        <v>0.421</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8115</v>
+        <v>-0.5637</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3866</v>
+        <v>-0.4338</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4151</v>
+        <v>0.3357</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8017</v>
+        <v>-0.7695</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2828</v>
+        <v>0.3665</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
         <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4346</v>
+        <v>0.5813</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3673</v>
+        <v>0.356</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0674</v>
+        <v>0.2253</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2508</v>
+        <v>0.0376</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8546</v>
+        <v>0.7585</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1055</v>
+        <v>-0.7209</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7084</v>
@@ -2014,13 +2014,13 @@
         <v>3.2986</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0188</v>
+        <v>0.2696</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9503</v>
+        <v>0.8541</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9691</v>
+        <v>-0.5845</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6231</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.276</v>
+        <v>-0.4815</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0906</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1855</v>
+        <v>0.2821</v>
       </c>
       <c r="G21" t="n">
         <v>-1.014</v>
@@ -2092,13 +2092,13 @@
         <v>2.7489</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9658</v>
+        <v>0.7604</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7564</v>
+        <v>1.0834</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7906</v>
+        <v>-0.323</v>
       </c>
       <c r="V21" t="n">
         <v>0.3219</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9871</v>
+        <v>-1.4392</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6581</v>
+        <v>-0.4658</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3289</v>
+        <v>-0.9734</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9116</v>
@@ -2170,13 +2170,13 @@
         <v>2.1991</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3925</v>
+        <v>0.1554</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1637</v>
+        <v>0.356</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5561</v>
+        <v>-0.2006</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3324</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4114</v>
+        <v>-2.3401</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7209</v>
+        <v>-1.6248</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6905</v>
+        <v>-0.7153</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5707</v>
@@ -2248,13 +2248,13 @@
         <v>0.3665</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0527</v>
+        <v>0.0187</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0551</v>
+        <v>0.0411</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0023</v>
+        <v>-0.0224</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3219</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.8779</v>
+        <v>9.083000000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>8.833</v>
+        <v>8.833099999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9551</v>
+        <v>0.2497999999999998</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1212</v>
@@ -2302,10 +2302,10 @@
         <v>10.8878</v>
       </c>
       <c r="K24" t="n">
-        <v>1.9087</v>
+        <v>1.908699999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>8.9788</v>
+        <v>8.978800000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-14.009</v>
@@ -2326,13 +2326,13 @@
         <v>19.2419</v>
       </c>
       <c r="S24" t="n">
-        <v>1.9231</v>
+        <v>5.1284</v>
       </c>
       <c r="T24" t="n">
-        <v>6.580100000000001</v>
+        <v>6.5803</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.657099999999999</v>
+        <v>-1.4519</v>
       </c>
       <c r="V24" t="n">
         <v>1.5783</v>
